--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,6 +129,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
@@ -227,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -292,19 +298,22 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1352,7 +1361,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1362,12 +1371,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1377,12 +1386,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1392,7 +1401,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3211,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3212,12 +3221,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -3227,12 +3236,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3242,7 +3251,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4540,27 +4549,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -4687,12 +4696,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 3641呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4950,27 +4959,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -5089,12 +5098,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>C | 4214呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -5353,32 +5362,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>

--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,12 +129,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
@@ -233,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -298,22 +292,19 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1361,23 +1352,19 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>236665000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>65000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1386,12 +1373,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1401,7 +1388,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3211,23 +3198,19 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>273910000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>65000</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3236,12 +3219,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3251,7 +3234,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4532,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4559,7 +4542,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4696,12 +4679,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 3641呎 (4+房)
-招标单位
--
-(在售)</t>
+$23666万
+$65,000/呎
+(26年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4942,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4969,7 +4952,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5098,12 +5081,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>C | 4214呎 (4+房)
-招标单位
--
-(在售)</t>
+$27391万
+$65,000/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -5362,32 +5345,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>

--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -4684,7 +4684,7 @@
           <t>B | 3641呎 (4+房)
 $23666万
 $65,000/呎
-(26年-10月-06日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
           <t>C | 4214呎 (4+房)
 $27391万
 $65,000/呎
-(26年-10月-06日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">

--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,6 +129,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
@@ -227,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -292,19 +298,22 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,7 +1221,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1222,12 +1231,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1237,12 +1246,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1252,7 +1261,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4532,27 +4541,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4665,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 3641呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5345,32 +5354,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
